--- a/data/trans_dic/P34A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,27; 48,65</t>
+          <t>41,31; 48,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 26,38</t>
+          <t>20,03; 26,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 39,14</t>
+          <t>31,65; 39,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,51; 42,98</t>
+          <t>34,45; 42,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,91; 45,3</t>
+          <t>37,39; 45,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,56</t>
+          <t>23,82; 30,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,28; 49,8</t>
+          <t>42,17; 49,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,36; 41,4</t>
+          <t>35,54; 41,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,66; 45,73</t>
+          <t>40,57; 45,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 27,57</t>
+          <t>22,7; 27,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,02; 43,74</t>
+          <t>38,19; 43,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,82; 41,06</t>
+          <t>35,92; 40,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 45,28</t>
+          <t>38,84; 45,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,01</t>
+          <t>21,47; 26,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 38,61</t>
+          <t>32,05; 38,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 34,36</t>
+          <t>13,44; 34,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,21; 50,42</t>
+          <t>43,79; 50,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,34; 39,23</t>
+          <t>33,09; 39,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,81; 46,13</t>
+          <t>40,12; 46,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,88; 41,51</t>
+          <t>35,71; 41,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,41; 47,03</t>
+          <t>42,36; 47,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,11; 32,31</t>
+          <t>28,02; 32,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,77; 41,23</t>
+          <t>36,69; 41,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,49; 36,48</t>
+          <t>20,41; 36,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 36,43</t>
+          <t>29,14; 36,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 23,98</t>
+          <t>17,85; 24,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,81</t>
+          <t>30,01; 37,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,48; 38,39</t>
+          <t>30,25; 38,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,35; 42,89</t>
+          <t>35,79; 43,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 31,59</t>
+          <t>24,97; 31,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 43,27</t>
+          <t>36,42; 43,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 49,8</t>
+          <t>19,48; 50,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,3; 38,67</t>
+          <t>33,2; 38,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,21; 27,1</t>
+          <t>22,18; 26,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,08; 39,16</t>
+          <t>33,99; 39,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 42,41</t>
+          <t>24,39; 42,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,15; 46,48</t>
+          <t>40,38; 46,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 24,53</t>
+          <t>19,1; 24,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 34,97</t>
+          <t>29,05; 35,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,3</t>
+          <t>25,93; 32,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,12; 56,39</t>
+          <t>50,13; 56,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,61; 33,11</t>
+          <t>27,24; 32,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,57; 45,81</t>
+          <t>39,24; 45,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,69; 41,57</t>
+          <t>31,3; 41,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,82; 50,27</t>
+          <t>46,08; 50,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 28,29</t>
+          <t>24,03; 28,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,57; 39,88</t>
+          <t>35,29; 39,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,21; 36,37</t>
+          <t>30,37; 36,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,54; 42,93</t>
+          <t>39,27; 42,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,1</t>
+          <t>21,01; 23,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,17; 35,48</t>
+          <t>32,23; 35,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,88</t>
+          <t>23,82; 34,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,33; 47,97</t>
+          <t>44,47; 47,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,53</t>
+          <t>29,39; 32,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,96; 44,33</t>
+          <t>41,07; 44,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,91; 41,08</t>
+          <t>30,79; 41,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,41; 44,94</t>
+          <t>42,38; 44,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,73; 27,8</t>
+          <t>25,69; 27,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,43</t>
+          <t>37,17; 39,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,08; 37,09</t>
+          <t>30,06; 36,99</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>283346; 334021</t>
+          <t>283620; 334378</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139382; 185323</t>
+          <t>140763; 189122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>211741; 264147</t>
+          <t>213577; 264932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>218388; 272029</t>
+          <t>218058; 271462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>259409; 309943</t>
+          <t>255847; 308781</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>163432; 212987</t>
+          <t>166059; 212918</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>284475; 335060</t>
+          <t>283703; 333046</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>238708; 279416</t>
+          <t>239912; 279296</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>557287; 626877</t>
+          <t>556156; 626866</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319114; 385950</t>
+          <t>317716; 382909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>512339; 589506</t>
+          <t>514652; 585395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>468440; 537061</t>
+          <t>469846; 535309</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>365467; 427865</t>
+          <t>367009; 429390</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>217382; 274926</t>
+          <t>218522; 273684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>332117; 394731</t>
+          <t>327719; 389775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174806; 408954</t>
+          <t>159968; 407707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>420893; 480059</t>
+          <t>416934; 480301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>344081; 404912</t>
+          <t>341551; 406766</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>415214; 481108</t>
+          <t>418435; 483421</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>343461; 397446</t>
+          <t>341853; 394875</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>804475; 892183</t>
+          <t>803654; 897253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>576230; 662423</t>
+          <t>574508; 660911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>759400; 851480</t>
+          <t>757817; 852983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>461589; 783420</t>
+          <t>438397; 783687</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>195485; 244199</t>
+          <t>195340; 242788</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135563; 181698</t>
+          <t>135227; 182717</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225450; 279576</t>
+          <t>227936; 281608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>214450; 270152</t>
+          <t>212816; 269594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>237277; 287892</t>
+          <t>240267; 289081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>192095; 245157</t>
+          <t>193773; 245187</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>283148; 339690</t>
+          <t>285882; 341704</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>178820; 463624</t>
+          <t>181353; 465653</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>446744; 518816</t>
+          <t>445430; 518588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>340692; 415570</t>
+          <t>340249; 409311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>526438; 604857</t>
+          <t>524974; 603625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>368607; 693280</t>
+          <t>398693; 698011</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>373321; 432168</t>
+          <t>375415; 433212</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>180558; 232275</t>
+          <t>180828; 232621</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>271296; 327861</t>
+          <t>272356; 330771</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>240220; 298414</t>
+          <t>239540; 297877</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>506827; 570211</t>
+          <t>506900; 568100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>290401; 348270</t>
+          <t>286486; 344475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>413040; 478115</t>
+          <t>409581; 479916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>334475; 452991</t>
+          <t>341081; 456696</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>889423; 975783</t>
+          <t>894327; 979543</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>482916; 565409</t>
+          <t>480300; 563969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>704838; 790196</t>
+          <t>699144; 783797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>608302; 732443</t>
+          <t>611493; 733128</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1277681; 1387470</t>
+          <t>1269057; 1384498</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>720971; 825293</t>
+          <t>719512; 820113</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1091965; 1204174</t>
+          <t>1093989; 1211924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>804984; 1168999</t>
+          <t>822048; 1173211</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1471330; 1592159</t>
+          <t>1475908; 1591174</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1042002; 1157285</t>
+          <t>1045472; 1157918</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1451762; 1571420</t>
+          <t>1455725; 1574322</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1129133; 1500600</t>
+          <t>1124899; 1504516</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2777688; 2943935</t>
+          <t>2775725; 2940722</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1796791; 1940903</t>
+          <t>1793702; 1945254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2570329; 2735966</t>
+          <t>2579108; 2745765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2136716; 2634551</t>
+          <t>2135725; 2627855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,31; 48,71</t>
+          <t>41,38; 49,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 26,92</t>
+          <t>20,09; 26,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,65; 39,26</t>
+          <t>31,65; 39,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,45; 42,89</t>
+          <t>34,74; 43,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,39; 45,13</t>
+          <t>37,79; 45,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 30,55</t>
+          <t>23,79; 30,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,17; 49,5</t>
+          <t>42,2; 49,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,54; 41,38</t>
+          <t>35,75; 41,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,57; 45,73</t>
+          <t>40,46; 45,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,7; 27,36</t>
+          <t>22,95; 27,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,19; 43,44</t>
+          <t>37,99; 43,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,92; 40,93</t>
+          <t>36,4; 41,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,84; 45,44</t>
+          <t>39,03; 45,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,47; 26,89</t>
+          <t>21,22; 27,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,05; 38,12</t>
+          <t>31,95; 37,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 34,26</t>
+          <t>30,06; 36,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,79; 50,45</t>
+          <t>43,5; 50,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,09; 39,41</t>
+          <t>33,35; 39,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,12; 46,35</t>
+          <t>39,68; 46,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,71; 41,25</t>
+          <t>35,6; 41,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,36; 47,3</t>
+          <t>42,26; 46,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,02; 32,24</t>
+          <t>28,26; 32,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,69; 41,3</t>
+          <t>36,82; 41,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,41; 36,49</t>
+          <t>33,62; 37,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 36,22</t>
+          <t>28,98; 36,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,12</t>
+          <t>17,66; 23,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,01; 37,08</t>
+          <t>29,91; 36,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,25; 38,31</t>
+          <t>31,68; 39,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 43,06</t>
+          <t>35,75; 42,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,97; 31,59</t>
+          <t>25,07; 32,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,42; 43,53</t>
+          <t>36,42; 43,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 50,01</t>
+          <t>41,92; 48,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,66</t>
+          <t>33,31; 38,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,18; 26,69</t>
+          <t>22,56; 27,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,99; 39,08</t>
+          <t>34,01; 39,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,39; 42,7</t>
+          <t>37,51; 42,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,38; 46,59</t>
+          <t>40,17; 46,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 24,57</t>
+          <t>19,19; 24,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 35,28</t>
+          <t>29,01; 35,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 32,24</t>
+          <t>25,54; 31,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,13; 56,18</t>
+          <t>50,0; 56,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,24; 32,75</t>
+          <t>27,74; 33,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,24; 45,98</t>
+          <t>39,64; 45,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,3; 41,91</t>
+          <t>38,1; 43,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,08; 50,47</t>
+          <t>45,99; 50,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 28,22</t>
+          <t>24,35; 28,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,29; 39,56</t>
+          <t>35,25; 39,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,37; 36,41</t>
+          <t>32,82; 36,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,27; 42,84</t>
+          <t>39,18; 42,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,01; 23,94</t>
+          <t>21,01; 23,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,23; 35,7</t>
+          <t>32,19; 35,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,82; 34,0</t>
+          <t>31,71; 35,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,94</t>
+          <t>44,36; 47,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,39; 32,55</t>
+          <t>29,27; 32,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,07; 44,42</t>
+          <t>41,15; 44,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,79; 41,18</t>
+          <t>39,14; 41,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,38; 44,89</t>
+          <t>42,42; 44,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,86</t>
+          <t>25,74; 27,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,17; 39,57</t>
+          <t>37,31; 39,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,06; 36,99</t>
+          <t>36,01; 38,11</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>268998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>258789</t>
+          <t>282673</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>502734</t>
+          <t>551671</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>283620; 334378</t>
+          <t>284112; 338112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>140763; 189122</t>
+          <t>141160; 186417</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>213577; 264932</t>
+          <t>213606; 264736</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>218058; 271462</t>
+          <t>238898; 297969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>255847; 308781</t>
+          <t>258553; 309320</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166059; 212918</t>
+          <t>165859; 213244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>283703; 333046</t>
+          <t>283959; 334504</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>239912; 279296</t>
+          <t>261837; 306136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>556156; 626866</t>
+          <t>554670; 626942</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>317716; 382909</t>
+          <t>321186; 388306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>514652; 585395</t>
+          <t>511938; 585820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>469846; 535309</t>
+          <t>516847; 586113</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>347265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>368422</t>
+          <t>410881</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>682014</t>
+          <t>758146</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>367009; 429390</t>
+          <t>368823; 429382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>218522; 273684</t>
+          <t>216057; 274893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>327719; 389775</t>
+          <t>326616; 387940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159968; 407707</t>
+          <t>314448; 382408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>416934; 480301</t>
+          <t>414124; 478692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>341551; 406766</t>
+          <t>344284; 407734</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>418435; 483421</t>
+          <t>413848; 480042</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>341853; 394875</t>
+          <t>380757; 439368</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>803654; 897253</t>
+          <t>801683; 886687</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>574508; 660911</t>
+          <t>579370; 663323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>757817; 852983</t>
+          <t>760513; 856507</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>438397; 783687</t>
+          <t>711233; 802327</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239711</t>
+          <t>281236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>347823</t>
+          <t>363584</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>587534</t>
+          <t>644819</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>195340; 242788</t>
+          <t>194257; 244011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135227; 182717</t>
+          <t>133810; 178940</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227936; 281608</t>
+          <t>227152; 279964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212816; 269594</t>
+          <t>254071; 314840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>240267; 289081</t>
+          <t>239992; 288234</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193773; 245187</t>
+          <t>194599; 248959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>285882; 341704</t>
+          <t>285921; 342027</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>181353; 465653</t>
+          <t>339321; 392056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>445430; 518588</t>
+          <t>446905; 518366</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>340249; 409311</t>
+          <t>345990; 414073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>524974; 603625</t>
+          <t>525249; 602873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>398693; 698011</t>
+          <t>604423; 686507</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268855</t>
+          <t>280806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>411977</t>
+          <t>451693</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>680832</t>
+          <t>732499</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>375415; 433212</t>
+          <t>373525; 435305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>180828; 232621</t>
+          <t>181672; 233007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>272356; 330771</t>
+          <t>271980; 329701</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>239540; 297877</t>
+          <t>252097; 311232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>506900; 568100</t>
+          <t>505542; 568334</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>286486; 344475</t>
+          <t>291849; 349422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>409581; 479916</t>
+          <t>413747; 478419</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>341081; 456696</t>
+          <t>424727; 480987</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>894327; 979543</t>
+          <t>892661; 980080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>480300; 563969</t>
+          <t>486746; 568759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>699144; 783797</t>
+          <t>698509; 784786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>611493; 733128</t>
+          <t>689752; 770251</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1269057; 1384498</t>
+          <t>1266243; 1378935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>719512; 820113</t>
+          <t>719529; 818528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1093989; 1211924</t>
+          <t>1092772; 1209112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>822048; 1173211</t>
+          <t>1117217; 1240274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1475908; 1591174</t>
+          <t>1472231; 1591192</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1045472; 1157918</t>
+          <t>1041111; 1153592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1455725; 1574322</t>
+          <t>1458520; 1578005</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1124899; 1504516</t>
+          <t>1458472; 1558289</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2775725; 2940722</t>
+          <t>2778487; 2944256</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1793702; 1945254</t>
+          <t>1797037; 1943348</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2579108; 2745765</t>
+          <t>2589110; 2748514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2135725; 2627855</t>
+          <t>2610556; 2762835</t>
         </is>
       </c>
     </row>
